--- a/donation_forms/018_tech_incubator_mentorship_donation_form--donation_forms.xlsx
+++ b/donation_forms/018_tech_incubator_mentorship_donation_form--donation_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,7 +441,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
     <col width="27" customWidth="1" min="3" max="3"/>
     <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -915,7 +915,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>how_did_you_find_us</t>
+          <t>how_did_you_find_us_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Email Confirmation</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1035,7 +1035,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Phone Confirmation</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Comments</t>
+          <t>Submit Comment</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1105,7 +1105,7 @@
   <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="29" customWidth="1" min="1" max="1"/>
+    <col width="31" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1232,7 +1232,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>how_did_you_find_us_choices</t>
+          <t>how_did_you_find_us_2_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1249,7 +1249,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>how_did_you_find_us_choices</t>
+          <t>how_did_you_find_us_2_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1266,7 +1266,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>how_did_you_find_us_choices</t>
+          <t>how_did_you_find_us_2_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1283,7 +1283,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>how_did_you_find_us_choices</t>
+          <t>how_did_you_find_us_2_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
